--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:22+00:00</t>
+    <t>2023-05-05T20:15:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:42+00:00</t>
+    <t>2023-05-05T20:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:19+00:00</t>
+    <t>2023-05-05T20:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:46+00:00</t>
+    <t>2023-05-05T20:33:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:33:04+00:00</t>
+    <t>2023-05-05T20:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:39:09+00:00</t>
+    <t>2023-05-05T20:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:44:23+00:00</t>
+    <t>2023-05-05T20:52:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:52:16+00:00</t>
+    <t>2023-05-05T21:01:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-06T12:19:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T07:05:14+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-09T07:17:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3510" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3508" uniqueCount="647">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T07:17:44+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -278,6 +278,9 @@
     <t>Act[classCode=PCPR, moodCode=INT]</t>
   </si>
   <si>
+    <t>clinical.careprovision</t>
+  </si>
+  <si>
     <t>CarePlan.id</t>
   </si>
   <si>
@@ -361,7 +364,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -419,6 +422,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -459,7 +466,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -478,7 +485,7 @@
     <t>Business identifiers assigned to this care plan by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
   </si>
   <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
   </si>
   <si>
     <t>Allows identification of the care plan as it is known by various participating systems and in a way that remains consistent across servers.</t>
@@ -518,205 +525,199 @@
     <t>CarePlan.identifier.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.use</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.id</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.id</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.coding</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.coding.id</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.coding.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.coding.system</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier:PLAC.type.coding.version</t>
+  </si>
+  <si>
+    <t>CarePlan.identifier.type.coding.version</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.use</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.id</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.id</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.coding</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.coding.id</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.coding.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.coding.system</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier:PLAC.type.coding.version</t>
-  </si>
-  <si>
-    <t>CarePlan.identifier.type.coding.version</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -892,7 +893,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1067,7 +1068,7 @@
     <t>Allows clinicians to determine whether the plan is actionable or not.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-status|4.3.0</t>
   </si>
   <si>
     <t>Request.status {uses different ValueSet}</t>
@@ -1100,7 +1101,7 @@
     <t>Codes indicating the degree of authority/intentionality associated with a care plan.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-intent|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-intent|4.3.0</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -1528,7 +1529,7 @@
     <t>The details of the proposed activity represented in a specific resource.</t>
   </si>
   <si>
-    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  +    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4B/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.   The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
   </si>
   <si>
@@ -1589,6 +1590,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>CarePlan.activity.detail.modifierExtension</t>
   </si>
   <si>
@@ -1610,7 +1615,7 @@
     <t>Resource types defined as part of FHIR that can be represented as in-line definitions of a care plan activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.3.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=LIST].code</t>
@@ -1757,7 +1762,7 @@
     <t>Codes that reflect the current state of a care plan activity within its overall life cycle.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-status|4.3.0</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -2602,7 +2607,7 @@
         <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>80</v>
@@ -2610,10 +2615,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2624,7 +2629,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>80</v>
@@ -2633,19 +2638,19 @@
         <v>80</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2695,13 +2700,13 @@
         <v>80</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>80</v>
@@ -2724,10 +2729,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2738,7 +2743,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>80</v>
@@ -2747,16 +2752,16 @@
         <v>80</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2807,19 +2812,19 @@
         <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
@@ -2836,10 +2841,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2850,28 +2855,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2921,19 +2926,19 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
@@ -2950,10 +2955,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2964,7 +2969,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>80</v>
@@ -2976,16 +2981,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3011,13 +3016,13 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>80</v>
@@ -3035,19 +3040,19 @@
         <v>80</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -3064,21 +3069,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>80</v>
@@ -3090,16 +3095,16 @@
         <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3149,25 +3154,25 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>80</v>
@@ -3178,14 +3183,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -3204,16 +3209,16 @@
         <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3263,7 +3268,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -3275,13 +3280,13 @@
         <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>80</v>
@@ -3292,14 +3297,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3318,16 +3323,16 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3377,7 +3382,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3389,13 +3394,13 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>80</v>
@@ -3406,14 +3411,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3426,25 +3431,25 @@
         <v>80</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>80</v>
@@ -3493,7 +3498,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3505,13 +3510,13 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>80</v>
@@ -3522,10 +3527,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3533,7 +3538,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>79</v>
@@ -3545,22 +3550,22 @@
         <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -3597,19 +3602,19 @@
         <v>80</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3621,40 +3626,40 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>80</v>
@@ -3663,22 +3668,22 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3727,7 +3732,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3739,27 +3744,27 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3770,7 +3775,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
@@ -3782,13 +3787,13 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3839,13 +3844,13 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>80</v>
@@ -3857,7 +3862,7 @@
         <v>80</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>80</v>
@@ -3868,14 +3873,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3894,16 +3899,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3941,19 +3946,19 @@
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3965,13 +3970,13 @@
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>80</v>
@@ -3982,10 +3987,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3996,31 +4001,31 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -4045,11 +4050,9 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y15" t="s" s="2">
         <v>180</v>
       </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>181</v>
       </c>
@@ -4075,13 +4078,13 @@
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
@@ -4093,7 +4096,7 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -4112,7 +4115,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>80</v>
@@ -4121,7 +4124,7 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>186</v>
@@ -4163,41 +4166,39 @@
       <c r="X16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>194</v>
-      </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
@@ -4209,15 +4210,15 @@
         <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4228,7 +4229,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -4240,13 +4241,13 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4297,13 +4298,13 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
@@ -4315,7 +4316,7 @@
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>80</v>
@@ -4326,14 +4327,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4352,16 +4353,16 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4399,19 +4400,19 @@
         <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4423,13 +4424,13 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>80</v>
@@ -4440,10 +4441,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4463,22 +4464,22 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4527,7 +4528,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4539,27 +4540,27 @@
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4570,7 +4571,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -4582,13 +4583,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4639,13 +4640,13 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
@@ -4657,7 +4658,7 @@
         <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>80</v>
@@ -4668,14 +4669,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4694,16 +4695,16 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4741,19 +4742,19 @@
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4765,13 +4766,13 @@
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>80</v>
@@ -4782,10 +4783,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4796,7 +4797,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>80</v>
@@ -4805,22 +4806,22 @@
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4830,78 +4831,78 @@
         <v>80</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="T22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF22" t="s" s="2">
+      <c r="AG22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AG22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4912,7 +4913,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>80</v>
@@ -4921,10 +4922,10 @@
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>226</v>
@@ -4989,13 +4990,13 @@
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
@@ -5026,7 +5027,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -5035,10 +5036,10 @@
         <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>234</v>
@@ -5058,7 +5059,7 @@
         <v>80</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>80</v>
@@ -5103,13 +5104,13 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
@@ -5140,7 +5141,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
@@ -5149,10 +5150,10 @@
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>242</v>
@@ -5217,13 +5218,13 @@
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
@@ -5254,7 +5255,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -5263,7 +5264,7 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>251</v>
@@ -5333,13 +5334,13 @@
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
@@ -5370,7 +5371,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
@@ -5379,10 +5380,10 @@
         <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>261</v>
@@ -5449,13 +5450,13 @@
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
@@ -5483,10 +5484,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -5495,10 +5496,10 @@
         <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>271</v>
@@ -5565,13 +5566,13 @@
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
@@ -5599,10 +5600,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
@@ -5611,10 +5612,10 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>282</v>
@@ -5679,13 +5680,13 @@
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -5716,7 +5717,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -5725,7 +5726,7 @@
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>291</v>
@@ -5791,13 +5792,13 @@
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
@@ -5828,7 +5829,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -5837,7 +5838,7 @@
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>299</v>
@@ -5905,13 +5906,13 @@
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
@@ -5951,7 +5952,7 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>307</v>
@@ -6023,7 +6024,7 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>310</v>
@@ -6063,10 +6064,10 @@
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>313</v>
@@ -6137,7 +6138,7 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>316</v>
@@ -6177,7 +6178,7 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>319</v>
@@ -6251,7 +6252,7 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>323</v>
@@ -6291,7 +6292,7 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>319</v>
@@ -6367,7 +6368,7 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>330</v>
@@ -6407,7 +6408,7 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>319</v>
@@ -6481,7 +6482,7 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
@@ -6509,22 +6510,22 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>336</v>
@@ -6561,7 +6562,7 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y37" t="s" s="2">
         <v>337</v>
@@ -6588,16 +6589,16 @@
         <v>335</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>341</v>
@@ -6625,22 +6626,22 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>346</v>
@@ -6677,7 +6678,7 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y38" t="s" s="2">
         <v>350</v>
@@ -6704,16 +6705,16 @@
         <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>352</v>
@@ -6753,7 +6754,7 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>186</v>
@@ -6829,7 +6830,7 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6860,7 +6861,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6869,10 +6870,10 @@
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>363</v>
@@ -6935,13 +6936,13 @@
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6972,7 +6973,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6981,10 +6982,10 @@
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>366</v>
@@ -7049,13 +7050,13 @@
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7083,10 +7084,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -7095,7 +7096,7 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>372</v>
@@ -7158,16 +7159,16 @@
         <v>370</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>375</v>
@@ -7195,10 +7196,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
@@ -7207,7 +7208,7 @@
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>380</v>
@@ -7275,13 +7276,13 @@
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>384</v>
@@ -7309,10 +7310,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
@@ -7321,7 +7322,7 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>291</v>
@@ -7391,13 +7392,13 @@
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>394</v>
@@ -7428,7 +7429,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -7437,7 +7438,7 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>400</v>
@@ -7503,13 +7504,13 @@
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>403</v>
@@ -7540,7 +7541,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
@@ -7549,7 +7550,7 @@
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>407</v>
@@ -7617,13 +7618,13 @@
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>411</v>
@@ -7737,7 +7738,7 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7851,7 +7852,7 @@
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>422</v>
@@ -7891,7 +7892,7 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>425</v>
@@ -7967,7 +7968,7 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>430</v>
@@ -8083,7 +8084,7 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>440</v>
@@ -8199,7 +8200,7 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -8227,7 +8228,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>79</v>
@@ -8344,7 +8345,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -8356,13 +8357,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8413,13 +8414,13 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
@@ -8431,7 +8432,7 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -8449,7 +8450,7 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8468,16 +8469,16 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8527,7 +8528,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8539,13 +8540,13 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8576,13 +8577,13 @@
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>460</v>
@@ -8591,10 +8592,10 @@
         <v>461</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8655,13 +8656,13 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8769,7 +8770,7 @@
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8885,7 +8886,7 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>474</v>
@@ -9001,7 +9002,7 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
@@ -9032,7 +9033,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -9111,13 +9112,13 @@
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>490</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>491</v>
@@ -9148,7 +9149,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
@@ -9225,7 +9226,7 @@
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>490</v>
@@ -9262,7 +9263,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
@@ -9274,13 +9275,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9331,13 +9332,13 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
@@ -9349,7 +9350,7 @@
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
@@ -9386,7 +9387,7 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>499</v>
@@ -9431,17 +9432,17 @@
         <v>80</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9453,7 +9454,7 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
@@ -9486,10 +9487,10 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>80</v>
@@ -9555,7 +9556,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9567,7 +9568,7 @@
         <v>506</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>138</v>
+        <v>507</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
@@ -9584,10 +9585,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9604,13 +9605,13 @@
         <v>80</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>460</v>
@@ -9619,10 +9620,10 @@
         <v>461</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9683,13 +9684,13 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
@@ -9700,10 +9701,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9714,10 +9715,10 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>80</v>
@@ -9726,17 +9727,17 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9746,7 +9747,7 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>80</v>
@@ -9761,13 +9762,13 @@
         <v>80</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>80</v>
@@ -9785,25 +9786,25 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
@@ -9814,10 +9815,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9840,17 +9841,17 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>308</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9899,7 +9900,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9911,7 +9912,7 @@
         <v>80</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>310</v>
@@ -9928,10 +9929,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9954,19 +9955,19 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>313</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>315</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10015,7 +10016,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10027,7 +10028,7 @@
         <v>80</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>316</v>
@@ -10044,10 +10045,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10058,10 +10059,10 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>80</v>
@@ -10073,16 +10074,16 @@
         <v>186</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10107,11 +10108,11 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10129,39 +10130,39 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10172,7 +10173,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>80</v>
@@ -10184,13 +10185,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10241,13 +10242,13 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>80</v>
@@ -10259,7 +10260,7 @@
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>80</v>
@@ -10270,14 +10271,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10296,16 +10297,16 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10343,19 +10344,19 @@
         <v>80</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10367,13 +10368,13 @@
         <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
@@ -10384,10 +10385,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10407,22 +10408,22 @@
         <v>80</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -10471,7 +10472,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10483,27 +10484,27 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10514,7 +10515,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>80</v>
@@ -10523,10 +10524,10 @@
         <v>80</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>261</v>
@@ -10548,7 +10549,7 @@
         <v>80</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>80</v>
@@ -10593,13 +10594,13 @@
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>80</v>
@@ -10616,10 +10617,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10630,10 +10631,10 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>80</v>
@@ -10645,13 +10646,13 @@
         <v>186</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10677,11 +10678,11 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10699,7 +10700,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10711,10 +10712,10 @@
         <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
@@ -10728,10 +10729,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10742,7 +10743,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>80</v>
@@ -10754,13 +10755,13 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10811,13 +10812,13 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>80</v>
@@ -10829,7 +10830,7 @@
         <v>80</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>80</v>
@@ -10840,14 +10841,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10866,16 +10867,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10913,19 +10914,19 @@
         <v>80</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10937,13 +10938,13 @@
         <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>80</v>
@@ -10954,10 +10955,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10977,22 +10978,22 @@
         <v>80</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11041,7 +11042,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11053,27 +11054,27 @@
         <v>80</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11084,7 +11085,7 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>80</v>
@@ -11093,10 +11094,10 @@
         <v>80</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>261</v>
@@ -11118,7 +11119,7 @@
         <v>80</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>80</v>
@@ -11163,13 +11164,13 @@
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>80</v>
@@ -11186,10 +11187,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11212,16 +11213,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11271,7 +11272,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11283,7 +11284,7 @@
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>430</v>
@@ -11300,10 +11301,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11329,14 +11330,14 @@
         <v>442</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11385,7 +11386,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11397,7 +11398,7 @@
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -11414,10 +11415,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11425,34 +11426,34 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11477,13 +11478,13 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -11501,39 +11502,39 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11544,7 +11545,7 @@
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>80</v>
@@ -11559,13 +11560,13 @@
         <v>186</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11615,22 +11616,22 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>80</v>
@@ -11644,10 +11645,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11658,13 +11659,13 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>80</v>
@@ -11673,85 +11674,85 @@
         <v>251</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q82" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="R82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M82" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q82" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="R82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>571</v>
-      </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>80</v>
@@ -11762,10 +11763,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11776,7 +11777,7 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>80</v>
@@ -11788,17 +11789,17 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -11835,29 +11836,29 @@
         <v>80</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>394</v>
@@ -11869,18 +11870,18 @@
         <v>80</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>80</v>
@@ -11890,7 +11891,7 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
@@ -11905,14 +11906,14 @@
         <v>291</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -11961,19 +11962,19 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>394</v>
@@ -11985,15 +11986,15 @@
         <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12004,7 +12005,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12016,19 +12017,19 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
@@ -12077,39 +12078,39 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12132,19 +12133,19 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12193,7 +12194,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12205,27 +12206,27 @@
         <v>80</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12236,7 +12237,7 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>80</v>
@@ -12248,13 +12249,13 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12284,61 +12285,61 @@
         <v>358</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>80</v>
@@ -12348,10 +12349,10 @@
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>80</v>
@@ -12363,10 +12364,10 @@
         <v>186</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12393,11 +12394,11 @@
         <v>80</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -12415,39 +12416,39 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12458,7 +12459,7 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>80</v>
@@ -12470,13 +12471,13 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12527,13 +12528,13 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>80</v>
@@ -12545,7 +12546,7 @@
         <v>80</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>80</v>
@@ -12556,14 +12557,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12582,16 +12583,16 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12629,19 +12630,19 @@
         <v>80</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12653,13 +12654,13 @@
         <v>80</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>80</v>
@@ -12670,10 +12671,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12693,22 +12694,22 @@
         <v>80</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -12757,7 +12758,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12769,27 +12770,27 @@
         <v>80</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12800,7 +12801,7 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>80</v>
@@ -12809,10 +12810,10 @@
         <v>80</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>261</v>
@@ -12834,7 +12835,7 @@
         <v>80</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>80</v>
@@ -12879,13 +12880,13 @@
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>80</v>
@@ -12902,21 +12903,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>80</v>
@@ -12928,17 +12929,17 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -12987,39 +12988,39 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13030,7 +13031,7 @@
         <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>80</v>
@@ -13042,13 +13043,13 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13099,39 +13100,39 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13142,7 +13143,7 @@
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>80</v>
@@ -13154,13 +13155,13 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13211,25 +13212,25 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>80</v>
@@ -13240,10 +13241,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13254,7 +13255,7 @@
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>80</v>
@@ -13269,14 +13270,14 @@
         <v>477</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -13325,7 +13326,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13337,10 +13338,10 @@
         <v>80</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>482</v>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3508" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3510" uniqueCount="646">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -278,9 +278,6 @@
     <t>Act[classCode=PCPR, moodCode=INT]</t>
   </si>
   <si>
-    <t>clinical.careprovision</t>
-  </si>
-  <si>
     <t>CarePlan.id</t>
   </si>
   <si>
@@ -364,7 +361,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -422,10 +419,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -466,7 +459,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -485,7 +478,7 @@
     <t>Business identifiers assigned to this care plan by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
   </si>
   <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
   </si>
   <si>
     <t>Allows identification of the care plan as it is known by various participating systems and in a way that remains consistent across servers.</t>
@@ -525,6 +518,10 @@
     <t>CarePlan.identifier.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -580,7 +577,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -614,6 +614,9 @@
     <t>extensible</t>
   </si>
   <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
@@ -714,10 +717,6 @@
     <t>CarePlan.identifier.type.coding.version</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -893,7 +892,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1068,7 +1067,7 @@
     <t>Allows clinicians to determine whether the plan is actionable or not.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
   </si>
   <si>
     <t>Request.status {uses different ValueSet}</t>
@@ -1101,7 +1100,7 @@
     <t>Codes indicating the degree of authority/intentionality associated with a care plan.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-intent|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-intent|4.0.1</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -1529,7 +1528,7 @@
     <t>The details of the proposed activity represented in a specific resource.</t>
   </si>
   <si>
-    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4B/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  +    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.   The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
   </si>
   <si>
@@ -1590,10 +1589,6 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>CarePlan.activity.detail.modifierExtension</t>
   </si>
   <si>
@@ -1615,7 +1610,7 @@
     <t>Resource types defined as part of FHIR that can be represented as in-line definitions of a care plan activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=LIST].code</t>
@@ -1762,7 +1757,7 @@
     <t>Codes that reflect the current state of a care plan activity within its overall life cycle.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-status|4.0.1</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -2607,7 +2602,7 @@
         <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>80</v>
@@ -2615,10 +2610,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2629,28 +2624,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2700,13 +2695,13 @@
         <v>80</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>80</v>
@@ -2729,10 +2724,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2743,25 +2738,25 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2812,19 +2807,19 @@
         <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
@@ -2841,10 +2836,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2855,28 +2850,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2926,19 +2921,19 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
@@ -2955,10 +2950,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2969,7 +2964,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>80</v>
@@ -2981,16 +2976,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3016,43 +3011,43 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -3069,21 +3064,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>80</v>
@@ -3095,16 +3090,16 @@
         <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3154,25 +3149,25 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>80</v>
@@ -3183,14 +3178,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -3209,16 +3204,16 @@
         <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3268,7 +3263,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -3280,13 +3275,13 @@
         <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>80</v>
@@ -3297,14 +3292,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3323,16 +3318,16 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3382,7 +3377,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3394,13 +3389,13 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>80</v>
@@ -3411,14 +3406,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3431,25 +3426,25 @@
         <v>80</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>80</v>
@@ -3498,7 +3493,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3510,13 +3505,13 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>80</v>
@@ -3527,10 +3522,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3538,7 +3533,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>79</v>
@@ -3550,22 +3545,22 @@
         <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -3602,19 +3597,19 @@
         <v>80</v>
       </c>
       <c r="AB11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AC11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>154</v>
-      </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3626,64 +3621,64 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>158</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K12" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3732,7 +3727,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3744,27 +3739,27 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>158</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3775,7 +3770,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
@@ -3787,13 +3782,13 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3844,25 +3839,25 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>80</v>
@@ -3873,14 +3868,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3899,16 +3894,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3946,19 +3941,19 @@
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC14" t="s" s="2">
+      <c r="AD14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AD14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE14" t="s" s="2">
+      <c r="AF14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3970,13 +3965,13 @@
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>80</v>
@@ -3987,10 +3982,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4001,31 +3996,31 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J15" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -4050,9 +4045,11 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>181</v>
       </c>
@@ -4078,13 +4075,13 @@
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
@@ -4096,7 +4093,7 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -4115,16 +4112,16 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>186</v>
@@ -4166,9 +4163,11 @@
       <c r="X16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Y16" s="2"/>
+      <c r="Y16" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -4186,19 +4185,19 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
@@ -4210,15 +4209,15 @@
         <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4229,7 +4228,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -4241,13 +4240,13 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4298,25 +4297,25 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>80</v>
@@ -4327,14 +4326,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4353,16 +4352,16 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4400,19 +4399,19 @@
         <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4424,13 +4423,13 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>80</v>
@@ -4441,10 +4440,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4464,22 +4463,22 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4528,7 +4527,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4540,27 +4539,27 @@
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4571,7 +4570,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -4583,13 +4582,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4640,25 +4639,25 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>80</v>
@@ -4669,14 +4668,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4695,16 +4694,16 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4742,19 +4741,19 @@
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC21" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC21" t="s" s="2">
+      <c r="AD21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE21" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AD21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE21" t="s" s="2">
+      <c r="AF21" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4766,13 +4765,13 @@
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>80</v>
@@ -4783,10 +4782,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4797,31 +4796,31 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4831,7 +4830,7 @@
         <v>80</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>80</v>
@@ -4870,39 +4869,39 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4913,19 +4912,19 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K23" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>226</v>
@@ -4990,13 +4989,13 @@
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
@@ -5027,19 +5026,19 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>234</v>
@@ -5059,7 +5058,7 @@
         <v>80</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>80</v>
@@ -5104,13 +5103,13 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
@@ -5141,19 +5140,19 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>242</v>
@@ -5218,13 +5217,13 @@
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
@@ -5255,16 +5254,16 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>251</v>
@@ -5334,13 +5333,13 @@
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
@@ -5371,19 +5370,19 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>261</v>
@@ -5450,13 +5449,13 @@
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
@@ -5484,22 +5483,22 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>271</v>
@@ -5566,13 +5565,13 @@
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
@@ -5600,22 +5599,22 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G29" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>282</v>
@@ -5680,13 +5679,13 @@
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -5717,16 +5716,16 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>291</v>
@@ -5792,13 +5791,13 @@
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
@@ -5829,16 +5828,16 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>299</v>
@@ -5906,13 +5905,13 @@
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
@@ -5952,7 +5951,7 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>307</v>
@@ -6024,7 +6023,7 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>310</v>
@@ -6064,10 +6063,10 @@
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>313</v>
@@ -6138,7 +6137,7 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>316</v>
@@ -6178,7 +6177,7 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>319</v>
@@ -6252,7 +6251,7 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>323</v>
@@ -6292,7 +6291,7 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>319</v>
@@ -6368,7 +6367,7 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>330</v>
@@ -6408,7 +6407,7 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>319</v>
@@ -6482,7 +6481,7 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
@@ -6510,22 +6509,22 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I37" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G37" t="s" s="2">
+      <c r="J37" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K37" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>336</v>
@@ -6562,7 +6561,7 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y37" t="s" s="2">
         <v>337</v>
@@ -6589,16 +6588,16 @@
         <v>335</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>341</v>
@@ -6626,22 +6625,22 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I38" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G38" t="s" s="2">
+      <c r="J38" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>346</v>
@@ -6678,7 +6677,7 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y38" t="s" s="2">
         <v>350</v>
@@ -6705,16 +6704,16 @@
         <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>352</v>
@@ -6754,7 +6753,7 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>186</v>
@@ -6830,7 +6829,7 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6861,19 +6860,19 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J40" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K40" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>363</v>
@@ -6936,13 +6935,13 @@
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6973,19 +6972,19 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K41" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>366</v>
@@ -7050,13 +7049,13 @@
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7084,19 +7083,19 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J42" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>372</v>
@@ -7159,16 +7158,16 @@
         <v>370</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>375</v>
@@ -7196,19 +7195,19 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J43" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>380</v>
@@ -7276,13 +7275,13 @@
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>384</v>
@@ -7310,19 +7309,19 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J44" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>291</v>
@@ -7392,13 +7391,13 @@
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>394</v>
@@ -7429,16 +7428,16 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J45" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>400</v>
@@ -7504,13 +7503,13 @@
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>403</v>
@@ -7541,16 +7540,16 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J46" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>407</v>
@@ -7618,13 +7617,13 @@
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>411</v>
@@ -7738,7 +7737,7 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7852,7 +7851,7 @@
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>422</v>
@@ -7892,7 +7891,7 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>425</v>
@@ -7968,7 +7967,7 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>430</v>
@@ -8084,7 +8083,7 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>440</v>
@@ -8200,7 +8199,7 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -8228,7 +8227,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>79</v>
@@ -8345,7 +8344,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -8357,13 +8356,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8414,25 +8413,25 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -8450,7 +8449,7 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8469,16 +8468,16 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8528,7 +8527,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8540,13 +8539,13 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8577,13 +8576,13 @@
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>460</v>
@@ -8592,10 +8591,10 @@
         <v>461</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8656,13 +8655,13 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8770,7 +8769,7 @@
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8886,7 +8885,7 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>474</v>
@@ -9002,7 +9001,7 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
@@ -9033,7 +9032,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -9112,13 +9111,13 @@
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>490</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>491</v>
@@ -9149,7 +9148,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
@@ -9226,7 +9225,7 @@
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>490</v>
@@ -9263,7 +9262,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
@@ -9275,13 +9274,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9332,25 +9331,25 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
@@ -9387,7 +9386,7 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>499</v>
@@ -9432,17 +9431,17 @@
         <v>80</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE62" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9454,7 +9453,7 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
@@ -9487,10 +9486,10 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H63" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>80</v>
@@ -9556,7 +9555,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9568,7 +9567,7 @@
         <v>506</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>507</v>
+        <v>138</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
@@ -9585,10 +9584,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9605,13 +9604,13 @@
         <v>80</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>460</v>
@@ -9620,10 +9619,10 @@
         <v>461</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9684,13 +9683,13 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
@@ -9701,10 +9700,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9715,11 +9714,11 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H65" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H65" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="I65" t="s" s="2">
         <v>80</v>
       </c>
@@ -9727,17 +9726,17 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9747,64 +9746,64 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y65" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="T65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y65" t="s" s="2">
+      <c r="Z65" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="Z65" t="s" s="2">
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
@@ -9815,10 +9814,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9841,17 +9840,17 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>308</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9900,7 +9899,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9912,7 +9911,7 @@
         <v>80</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>310</v>
@@ -9929,10 +9928,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9955,19 +9954,19 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>313</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>315</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10016,7 +10015,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10028,7 +10027,7 @@
         <v>80</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>316</v>
@@ -10045,10 +10044,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10059,10 +10058,10 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H68" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>80</v>
@@ -10074,16 +10073,16 @@
         <v>186</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10108,61 +10107,61 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK68" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AA68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK68" t="s" s="2">
+      <c r="AL68" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>531</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10173,7 +10172,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>80</v>
@@ -10185,13 +10184,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10242,25 +10241,25 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>80</v>
@@ -10271,14 +10270,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10297,16 +10296,16 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10344,19 +10343,19 @@
         <v>80</v>
       </c>
       <c r="AB70" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC70" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC70" t="s" s="2">
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AD70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE70" t="s" s="2">
+      <c r="AF70" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10368,13 +10367,13 @@
         <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
@@ -10385,10 +10384,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10408,22 +10407,22 @@
         <v>80</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -10472,7 +10471,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10484,27 +10483,27 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10515,19 +10514,19 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J72" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K72" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>261</v>
@@ -10549,7 +10548,7 @@
         <v>80</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>80</v>
@@ -10594,13 +10593,13 @@
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>80</v>
@@ -10617,10 +10616,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10631,10 +10630,10 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H73" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>80</v>
@@ -10646,13 +10645,13 @@
         <v>186</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10678,11 +10677,11 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10700,7 +10699,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10712,10 +10711,10 @@
         <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
@@ -10729,10 +10728,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10743,7 +10742,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>80</v>
@@ -10755,13 +10754,13 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10812,25 +10811,25 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>80</v>
@@ -10841,14 +10840,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10867,16 +10866,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10914,19 +10913,19 @@
         <v>80</v>
       </c>
       <c r="AB75" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC75" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC75" t="s" s="2">
+      <c r="AD75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE75" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AD75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE75" t="s" s="2">
+      <c r="AF75" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10938,13 +10937,13 @@
         <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>80</v>
@@ -10955,10 +10954,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10978,22 +10977,22 @@
         <v>80</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11042,7 +11041,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11054,27 +11053,27 @@
         <v>80</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11085,19 +11084,19 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J77" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K77" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>261</v>
@@ -11119,7 +11118,7 @@
         <v>80</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>80</v>
@@ -11164,13 +11163,13 @@
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>80</v>
@@ -11187,10 +11186,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11213,16 +11212,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11272,7 +11271,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11284,7 +11283,7 @@
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>430</v>
@@ -11301,10 +11300,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11330,14 +11329,14 @@
         <v>442</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11386,7 +11385,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11398,7 +11397,7 @@
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -11415,10 +11414,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11426,34 +11425,34 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I80" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G80" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11478,63 +11477,63 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="Z80" t="s" s="2">
+      <c r="AA80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK80" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AA80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK80" t="s" s="2">
+      <c r="AL80" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AL80" t="s" s="2">
+      <c r="AM80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>566</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11545,7 +11544,7 @@
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>80</v>
@@ -11560,13 +11559,13 @@
         <v>186</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11616,22 +11615,22 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>80</v>
@@ -11645,10 +11644,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11659,13 +11658,13 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I82" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>80</v>
@@ -11674,85 +11673,85 @@
         <v>251</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="O82" t="s" s="2">
+      <c r="P82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q82" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="P82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q82" t="s" s="2">
+      <c r="R82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK82" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="R82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK82" t="s" s="2">
+      <c r="AL82" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>80</v>
@@ -11763,10 +11762,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11777,7 +11776,7 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>80</v>
@@ -11789,17 +11788,17 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -11836,29 +11835,29 @@
         <v>80</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>394</v>
@@ -11870,18 +11869,18 @@
         <v>80</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>80</v>
@@ -11891,7 +11890,7 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
@@ -11906,14 +11905,14 @@
         <v>291</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -11962,19 +11961,19 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>394</v>
@@ -11986,15 +11985,15 @@
         <v>80</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12005,7 +12004,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12017,19 +12016,19 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
@@ -12078,39 +12077,39 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>596</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12133,19 +12132,19 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="N86" t="s" s="2">
-        <v>601</v>
-      </c>
       <c r="O86" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12194,7 +12193,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12206,27 +12205,27 @@
         <v>80</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AL86" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="AL86" t="s" s="2">
+      <c r="AM86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>604</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12237,7 +12236,7 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>80</v>
@@ -12249,13 +12248,13 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12285,61 +12284,61 @@
         <v>358</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="Z87" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="Z87" t="s" s="2">
-        <v>610</v>
-      </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>612</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>80</v>
@@ -12349,10 +12348,10 @@
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H88" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>80</v>
@@ -12364,10 +12363,10 @@
         <v>186</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12394,11 +12393,11 @@
         <v>80</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -12416,39 +12415,39 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>612</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12459,7 +12458,7 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>80</v>
@@ -12471,13 +12470,13 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12528,25 +12527,25 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL89" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>80</v>
@@ -12557,14 +12556,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12583,16 +12582,16 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12630,19 +12629,19 @@
         <v>80</v>
       </c>
       <c r="AB90" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AC90" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC90" t="s" s="2">
+      <c r="AD90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE90" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AD90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE90" t="s" s="2">
+      <c r="AF90" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12654,13 +12653,13 @@
         <v>80</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>80</v>
@@ -12671,10 +12670,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12694,22 +12693,22 @@
         <v>80</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -12758,7 +12757,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12770,27 +12769,27 @@
         <v>80</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12801,19 +12800,19 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J92" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K92" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>261</v>
@@ -12835,7 +12834,7 @@
         <v>80</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>80</v>
@@ -12880,13 +12879,13 @@
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>80</v>
@@ -12903,21 +12902,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>80</v>
@@ -12929,17 +12928,17 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -12988,39 +12987,39 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>632</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13031,7 +13030,7 @@
         <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>80</v>
@@ -13043,13 +13042,13 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13100,39 +13099,39 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>637</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13143,7 +13142,7 @@
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>80</v>
@@ -13155,13 +13154,13 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13212,25 +13211,25 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>80</v>
@@ -13241,10 +13240,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13255,7 +13254,7 @@
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>80</v>
@@ -13270,14 +13269,14 @@
         <v>477</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -13326,7 +13325,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13338,10 +13337,10 @@
         <v>80</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>482</v>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$59</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2430" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1559,110 +1559,6 @@
   </si>
   <si>
     <t>{Request that resulted in Event in activity.performedActivity}</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.id</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.extension:artRegimenSwitchedOrSubstituted</t>
-  </si>
-  <si>
-    <t>artRegimenSwitchedOrSubstituted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/art-regimen-switched-or-substituted}
-</t>
-  </si>
-  <si>
-    <t>ART Regimen Switched Or Substituted</t>
-  </si>
-  <si>
-    <t>The ARV regimen has been switched to a new ARV regimen or has been substituted by another ARV regimen.</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t>ref-2
-ref-1</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient") - must be a resource in resources</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a known RESTful URL) or by resolving the target of the reference.</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).
-This element only allows for a single identifier. In the case where additional identifers are required, use the [http://hl7.org/fhir/StructureDefinition/additionalIdentifier](http://hl7.org/fhir/extensions/StructureDefinition-additionalIdentifier.html) extension.</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-2
-</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.plannedActivityReference.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
   </si>
   <si>
     <t>CarePlan.note</t>
@@ -2002,12 +1898,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN66"/>
+  <dimension ref="A1:AN59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="82.83984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="32.90625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="47.23828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.95703125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2015,7 +1911,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="96.05078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="87.99609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -7985,7 +7881,7 @@
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>462</v>
@@ -8675,7 +8571,7 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>495</v>
@@ -8706,10 +8602,10 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>80</v>
@@ -8718,16 +8614,18 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>90</v>
+        <v>482</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>164</v>
+        <v>497</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>165</v>
+        <v>498</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -8775,833 +8673,35 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>166</v>
+        <v>496</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>168</v>
+        <v>487</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="D61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AN66" t="s" s="2">
         <v>488</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN66">
+  <autoFilter ref="A1:AN59">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9611,7 +8711,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI58">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -495,7 +495,7 @@
     <t>Allows identification of the care plan as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">exists:system}
 </t>
   </si>
   <si>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -495,7 +495,7 @@
     <t>Allows identification of the care plan as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
-    <t xml:space="preserve">exists:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="500">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -502,7 +502,7 @@
     <t>Slice based on the type of identifier.</t>
   </si>
   <si>
-    <t>openAtEnd</t>
+    <t>open</t>
   </si>
   <si>
     <t>Request.identifier</t>
@@ -559,9 +559,6 @@
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -3518,10 +3515,10 @@
         <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3550,10 +3547,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3579,16 +3576,16 @@
         <v>108</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3616,28 +3613,28 @@
         <v>112</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3658,7 +3655,7 @@
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>133</v>
@@ -3666,10 +3663,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3692,19 +3689,19 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3729,31 +3726,31 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3774,18 +3771,18 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3894,10 +3891,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3976,10 +3973,10 @@
         <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4008,10 +4005,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4034,19 +4031,19 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4095,7 +4092,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4116,18 +4113,18 @@
         <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4236,10 +4233,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4318,10 +4315,10 @@
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4350,10 +4347,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4379,16 +4376,16 @@
         <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4398,46 +4395,46 @@
         <v>80</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4458,18 +4455,18 @@
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4492,16 +4489,16 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4551,7 +4548,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4572,18 +4569,18 @@
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4609,14 +4606,14 @@
         <v>108</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4665,7 +4662,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4674,7 +4671,7 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>100</v>
@@ -4686,18 +4683,18 @@
         <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4720,17 +4717,17 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4740,46 +4737,46 @@
         <v>80</v>
       </c>
       <c r="S25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4788,7 +4785,7 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>100</v>
@@ -4800,18 +4797,18 @@
         <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4834,19 +4831,19 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4895,7 +4892,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4916,18 +4913,18 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4950,19 +4947,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4972,46 +4969,46 @@
         <v>80</v>
       </c>
       <c r="S27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5032,18 +5029,18 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5069,65 +5066,65 @@
         <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T28" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="S28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T28" t="s" s="2">
+      <c r="U28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5148,18 +5145,18 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5182,16 +5179,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5205,43 +5202,43 @@
         <v>80</v>
       </c>
       <c r="T29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5250,7 +5247,7 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>100</v>
@@ -5262,18 +5259,18 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5296,13 +5293,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5353,7 +5350,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5374,18 +5371,18 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5408,16 +5405,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5467,7 +5464,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5488,18 +5485,18 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5522,13 +5519,13 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5579,7 +5576,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5594,13 +5591,13 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5608,10 +5605,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5637,13 +5634,13 @@
         <v>102</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5693,7 +5690,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5708,13 +5705,13 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5722,14 +5719,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5748,17 +5745,17 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5807,7 +5804,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5822,7 +5819,7 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>80</v>
@@ -5836,14 +5833,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5862,19 +5859,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -5923,7 +5920,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5938,7 +5935,7 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
@@ -5952,10 +5949,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5978,16 +5975,16 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6037,7 +6034,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6066,10 +6063,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6095,16 +6092,16 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6132,10 +6129,10 @@
         <v>112</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6153,7 +6150,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -6168,24 +6165,24 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6211,16 +6208,16 @@
         <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6248,11 +6245,11 @@
         <v>112</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6269,7 +6266,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>88</v>
@@ -6284,7 +6281,7 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>80</v>
@@ -6298,10 +6295,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6324,19 +6321,19 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6361,14 +6358,14 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="Y39" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="Y39" t="s" s="2">
+      <c r="Z39" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>366</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6385,7 +6382,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6403,7 +6400,7 @@
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
@@ -6414,10 +6411,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6440,13 +6437,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6497,7 +6494,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6526,10 +6523,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6552,17 +6549,17 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6611,7 +6608,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6629,7 +6626,7 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
@@ -6640,14 +6637,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6666,13 +6663,13 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6723,7 +6720,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>88</v>
@@ -6738,24 +6735,24 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6778,16 +6775,16 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6837,7 +6834,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6852,28 +6849,28 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>393</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6892,19 +6889,19 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -6953,7 +6950,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6968,28 +6965,28 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>403</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7008,13 +7005,13 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7065,7 +7062,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7080,13 +7077,13 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
@@ -7094,10 +7091,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7120,16 +7117,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7179,7 +7176,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7194,10 +7191,10 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
@@ -7208,10 +7205,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7234,16 +7231,16 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7293,7 +7290,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7322,10 +7319,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7348,17 +7345,17 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7407,7 +7404,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7422,10 +7419,10 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
@@ -7436,10 +7433,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7462,19 +7459,19 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7499,14 +7496,14 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7523,7 +7520,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7538,24 +7535,24 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>441</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7578,19 +7575,19 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7639,7 +7636,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7654,7 +7651,7 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>80</v>
@@ -7668,10 +7665,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7694,19 +7691,19 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7755,7 +7752,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7776,18 +7773,18 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>456</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7810,17 +7807,17 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7869,7 +7866,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7884,13 +7881,13 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -7898,10 +7895,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7924,7 +7921,7 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>164</v>
@@ -8010,10 +8007,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8095,7 +8092,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8124,14 +8121,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8153,10 +8150,10 @@
         <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>139</v>
@@ -8211,7 +8208,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8240,10 +8237,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8266,19 +8263,19 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8303,14 +8300,14 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>478</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8327,7 +8324,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8342,13 +8339,13 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8356,10 +8353,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8382,19 +8379,19 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8443,7 +8440,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8464,18 +8461,18 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>488</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8498,19 +8495,19 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8559,7 +8556,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8574,13 +8571,13 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -8588,10 +8585,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8614,17 +8611,17 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8673,7 +8670,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8688,16 +8685,16 @@
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-arv-treatment</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/hiv-arv-treatment</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/hiv-arv-treatment</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-arv-treatment</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-arv-treatment</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/hiv-arv-treatment</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/hiv-arv-treatment</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-arv-treatment</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:13:26+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/StructureDefinition-hiv-arv-treatment.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="460">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:20:07+00:00</t>
+    <t>2023-07-05T16:42:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,126 +127,6 @@
   </si>
   <si>
     <t>constraint</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Slice Name</t>
-  </si>
-  <si>
-    <t>Alias(s)</t>
-  </si>
-  <si>
-    <t>Label</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Must Support?</t>
-  </si>
-  <si>
-    <t>Is Modifier?</t>
-  </si>
-  <si>
-    <t>Is Summary?</t>
-  </si>
-  <si>
-    <t>Type(s)</t>
-  </si>
-  <si>
-    <t>Short</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Requirements</t>
-  </si>
-  <si>
-    <t>Default Value</t>
-  </si>
-  <si>
-    <t>Meaning When Missing</t>
-  </si>
-  <si>
-    <t>Fixed Value</t>
-  </si>
-  <si>
-    <t>Pattern</t>
-  </si>
-  <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>Minimum Value</t>
-  </si>
-  <si>
-    <t>Maximum Value</t>
-  </si>
-  <si>
-    <t>Maximum Length</t>
-  </si>
-  <si>
-    <t>Binding Strength</t>
-  </si>
-  <si>
-    <t>Binding Description</t>
-  </si>
-  <si>
-    <t>Binding Value Set</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Slicing Discriminator</t>
-  </si>
-  <si>
-    <t>Slicing Description</t>
-  </si>
-  <si>
-    <t>Slicing Ordered</t>
-  </si>
-  <si>
-    <t>Slicing Rules</t>
-  </si>
-  <si>
-    <t>Base Path</t>
-  </si>
-  <si>
-    <t>Base Min</t>
-  </si>
-  <si>
-    <t>Base Max</t>
-  </si>
-  <si>
-    <t>Condition(s)</t>
-  </si>
-  <si>
-    <t>Constraint(s)</t>
-  </si>
-  <si>
-    <t>Mapping: Workflow Pattern</t>
-  </si>
-  <si>
-    <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: RIM Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: HL7 V2 Mapping</t>
   </si>
   <si>
     <t xml:space="preserve">Care Team
@@ -1692,10 +1572,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -1895,18 +1775,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN59"/>
+  <dimension ref="A1:AN58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.23828125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.95703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="5.70703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="2.2109375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="2.2109375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="2.1640625" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="87.99609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1914,6791 +1793,6669 @@
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="158.5078125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.58984375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="14.46484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="40.80859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="33" max="33" width="2.2109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="20.703125" customWidth="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="67.90625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="20.359375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="45.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="1">
+      <c r="A1" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>38</v>
-      </c>
-      <c r="C1" t="s" s="1">
+      <c r="E1" s="2"/>
+      <c r="F1" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>40</v>
-      </c>
-      <c r="E1" t="s" s="1">
+      <c r="H1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K1" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="L1" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="M1" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q1" s="2"/>
+      <c r="R1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF1" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH1" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AK1" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="AL1" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="AM1" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="K1" t="s" s="1">
-        <v>47</v>
-      </c>
-      <c r="L1" t="s" s="1">
-        <v>48</v>
-      </c>
-      <c r="M1" t="s" s="1">
-        <v>49</v>
-      </c>
-      <c r="N1" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="O1" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="P1" t="s" s="1">
-        <v>52</v>
-      </c>
-      <c r="Q1" t="s" s="1">
-        <v>53</v>
-      </c>
-      <c r="R1" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="S1" t="s" s="1">
-        <v>55</v>
-      </c>
-      <c r="T1" t="s" s="1">
-        <v>56</v>
-      </c>
-      <c r="U1" t="s" s="1">
-        <v>57</v>
-      </c>
-      <c r="V1" t="s" s="1">
-        <v>58</v>
-      </c>
-      <c r="W1" t="s" s="1">
-        <v>59</v>
-      </c>
-      <c r="X1" t="s" s="1">
-        <v>60</v>
-      </c>
-      <c r="Y1" t="s" s="1">
-        <v>61</v>
-      </c>
-      <c r="Z1" t="s" s="1">
-        <v>62</v>
-      </c>
-      <c r="AA1" t="s" s="1">
-        <v>63</v>
-      </c>
-      <c r="AB1" t="s" s="1">
-        <v>64</v>
-      </c>
-      <c r="AC1" t="s" s="1">
-        <v>65</v>
-      </c>
-      <c r="AD1" t="s" s="1">
-        <v>66</v>
-      </c>
-      <c r="AE1" t="s" s="1">
-        <v>67</v>
-      </c>
-      <c r="AF1" t="s" s="1">
-        <v>68</v>
-      </c>
-      <c r="AG1" t="s" s="1">
-        <v>69</v>
-      </c>
-      <c r="AH1" t="s" s="1">
-        <v>70</v>
-      </c>
-      <c r="AI1" t="s" s="1">
-        <v>71</v>
-      </c>
-      <c r="AJ1" t="s" s="1">
-        <v>72</v>
-      </c>
-      <c r="AK1" t="s" s="1">
-        <v>73</v>
-      </c>
-      <c r="AL1" t="s" s="1">
-        <v>74</v>
-      </c>
-      <c r="AM1" t="s" s="1">
-        <v>75</v>
-      </c>
-      <c r="AN1" t="s" s="1">
-        <v>76</v>
+      <c r="AN1" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="N2" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="N2" t="s" s="2">
+        <v>53</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N4" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="N4" t="s" s="2">
+        <v>65</v>
+      </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G6" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H6" t="s" s="2">
+      <c r="L6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="I6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>110</v>
-      </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="M7" t="s" s="2">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O9" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="O9" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="P9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>154</v>
+        <v>40</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>159</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>40</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>159</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>97</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>99</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>137</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="O14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="P15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>50</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>124</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>192</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>193</v>
+        <v>40</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>194</v>
+        <v>40</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>184</v>
+        <v>128</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>196</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>164</v>
+        <v>97</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>99</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="P18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>50</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>124</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>126</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>209</v>
+        <v>128</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>210</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>164</v>
+        <v>97</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>99</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="P21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>80</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>221</v>
+        <v>40</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>191</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>224</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>227</v>
+        <v>68</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>233</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>204</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="P24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>242</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="P25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>248</v>
+        <v>40</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>251</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>254</v>
+        <v>187</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>258</v>
+        <v>227</v>
       </c>
       <c r="P26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>227</v>
+        <v>62</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>267</v>
+        <v>237</v>
       </c>
       <c r="P27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>80</v>
+        <v>238</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>268</v>
+        <v>40</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>80</v>
+        <v>239</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>271</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>278</v>
+        <v>40</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>279</v>
+        <v>248</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>282</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>288</v>
+        <v>40</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>290</v>
+        <v>40</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>291</v>
+        <v>259</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>292</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>295</v>
+        <v>263</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>300</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>303</v>
+        <v>271</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>309</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>310</v>
+        <v>276</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>310</v>
+        <v>276</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>311</v>
+        <v>62</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>312</v>
+        <v>277</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>310</v>
+        <v>276</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>314</v>
+        <v>280</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>281</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>102</v>
+        <v>283</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>281</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>40</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="P34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>329</v>
+        <v>40</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
+        <v>298</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>335</v>
+        <v>40</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>330</v>
+        <v>68</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>337</v>
+        <v>301</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>338</v>
+        <v>302</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>80</v>
+        <v>306</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>80</v>
+        <v>307</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>80</v>
+        <v>308</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>80</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>344</v>
+        <v>314</v>
       </c>
       <c r="P37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>347</v>
+        <v>40</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>348</v>
+        <v>40</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>349</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="P38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>112</v>
+        <v>323</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>357</v>
+        <v>40</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>80</v>
+        <v>326</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>359</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>363</v>
+        <v>40</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>364</v>
+        <v>40</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>365</v>
+        <v>40</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>366</v>
+        <v>40</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>367</v>
+        <v>330</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>367</v>
+        <v>330</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>368</v>
+        <v>331</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>369</v>
+        <v>332</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>367</v>
+        <v>330</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>80</v>
+        <v>336</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>227</v>
+        <v>337</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>371</v>
+        <v>338</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>373</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>374</v>
+        <v>341</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>80</v>
+        <v>343</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>376</v>
+        <v>40</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>380</v>
+        <v>349</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>383</v>
+        <v>352</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>384</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>384</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>80</v>
+        <v>354</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>385</v>
+        <v>255</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="P43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>384</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>391</v>
+        <v>361</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>392</v>
+        <v>362</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>395</v>
+        <v>366</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>401</v>
+        <v>370</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>402</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>404</v>
+        <v>40</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>405</v>
+        <v>372</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>406</v>
+        <v>373</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>409</v>
+        <v>377</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>410</v>
+        <v>40</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>413</v>
+        <v>379</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>414</v>
+        <v>380</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>416</v>
+        <v>40</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>417</v>
+        <v>40</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>412</v>
+        <v>383</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>419</v>
+        <v>384</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>80</v>
+        <v>387</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>80</v>
+        <v>388</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="P48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>80</v>
+        <v>396</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>80</v>
+        <v>399</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>80</v>
+        <v>400</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>431</v>
+        <v>403</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>363</v>
+        <v>40</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>435</v>
+        <v>40</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>436</v>
+        <v>40</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>438</v>
+        <v>40</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>439</v>
+        <v>40</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>440</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>441</v>
+        <v>408</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>441</v>
+        <v>408</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>442</v>
+        <v>409</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>444</v>
+        <v>411</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>446</v>
+        <v>413</v>
       </c>
       <c r="P50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>441</v>
+        <v>408</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>447</v>
+        <v>40</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>80</v>
+        <v>414</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>416</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>416</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>449</v>
+        <v>417</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>450</v>
+        <v>418</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>453</v>
+        <v>420</v>
       </c>
       <c r="P51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>448</v>
+        <v>416</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>454</v>
+        <v>422</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>455</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>423</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>456</v>
+        <v>423</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>457</v>
+        <v>187</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>458</v>
+        <v>124</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>459</v>
+        <v>125</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>456</v>
+        <v>126</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>461</v>
+        <v>40</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>462</v>
+        <v>128</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>463</v>
+        <v>424</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>463</v>
+        <v>424</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>227</v>
+        <v>96</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>164</v>
+        <v>97</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>99</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>464</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>464</v>
+        <v>425</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>135</v>
+        <v>426</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>137</v>
+        <v>427</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>171</v>
+        <v>428</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="P54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>174</v>
+        <v>429</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>168</v>
+        <v>93</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>465</v>
+        <v>430</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>465</v>
+        <v>430</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>466</v>
+        <v>40</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>136</v>
+        <v>431</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>467</v>
+        <v>432</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>468</v>
+        <v>433</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>139</v>
+        <v>434</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>145</v>
+        <v>435</v>
       </c>
       <c r="P55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>80</v>
+        <v>437</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>469</v>
+        <v>430</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>80</v>
+        <v>438</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>133</v>
+        <v>439</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>474</v>
+        <v>444</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="P56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>363</v>
+        <v>40</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>476</v>
+        <v>40</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>477</v>
+        <v>40</v>
       </c>
       <c r="AA56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>478</v>
+        <v>40</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>80</v>
+        <v>447</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>481</v>
+        <v>449</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>482</v>
+        <v>450</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>484</v>
+        <v>452</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>485</v>
+        <v>453</v>
       </c>
       <c r="P57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>80</v>
+        <v>454</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>486</v>
+        <v>422</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>487</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>489</v>
+        <v>441</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>490</v>
+        <v>456</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>493</v>
+        <v>458</v>
       </c>
       <c r="P58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="U58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="W58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>494</v>
+        <v>459</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>487</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN59">
+  <autoFilter ref="A1:AN58">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8708,7 +8465,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI58">
+  <conditionalFormatting sqref="A2:AI57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
